--- a/Recursos/MATRICULADOS.xlsx
+++ b/Recursos/MATRICULADOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\UNI\UNI-FIIS-2025-2-BIC01-U\Recursos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAFE649-DEB7-4080-8875-890016C46E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE1CD17-3410-4DCB-A55A-829E4DDAA1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="96">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>27.SET</t>
   </si>
 </sst>
 </file>
@@ -458,16 +461,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -492,6 +485,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Énfasis1" xfId="1" builtinId="29"/>
@@ -878,15 +881,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
@@ -1520,377 +1523,435 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E36106-38C0-4313-B1A4-BF1C2EC0CF13}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
-    <col min="4" max="4" width="14" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="12" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
+      <c r="E1" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11">
+      <c r="D2" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11">
+      <c r="D3" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11">
+      <c r="D4" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11">
+      <c r="D5" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11">
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11">
+      <c r="D7" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11">
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11">
+      <c r="D9" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="11" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11">
+      <c r="D10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11">
+      <c r="D11" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11">
+      <c r="D12" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11">
-        <v>13</v>
-      </c>
-      <c r="B14" s="11" t="s">
+      <c r="D13" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="s">
+      <c r="D14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="13"/>
-    </row>
-    <row r="16" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+    </row>
+    <row r="16" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11">
+      <c r="D16" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11">
+      <c r="D17" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="9"/>
+    </row>
+    <row r="18" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11">
+      <c r="D18" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11">
+      <c r="D19" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="9"/>
+    </row>
+    <row r="20" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="13"/>
-    </row>
-    <row r="21" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11">
+      <c r="D20" s="9"/>
+      <c r="E20" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11">
+      <c r="D21" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11">
+      <c r="D22" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11">
+      <c r="D23" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11">
+      <c r="D24" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="9"/>
+    </row>
+    <row r="25" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11">
+      <c r="D25" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="7">
         <v>25</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="13"/>
-    </row>
-    <row r="27" spans="1:4" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="11">
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+    </row>
+    <row r="27" spans="1:5" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="7">
         <v>26</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>94</v>
       </c>
     </row>
